--- a/Result/profitability/2369.xlsx
+++ b/Result/profitability/2369.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1625</v>
+        <v>-0.10625</v>
       </c>
       <c r="N2" t="n">
-        <v>1.38125</v>
+        <v>2.77</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10125</v>
+        <v>-0.04874999999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3325</v>
+        <v>4.87125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01374999999999998</v>
+        <v>0.04875000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>5.96375</v>
+        <v>7.697500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008750000000000022</v>
+        <v>0.07875000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>7.305000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02625000000000002</v>
+        <v>0.09125000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>7.57875</v>
+        <v>9.36125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08375000000000002</v>
+        <v>0.1175</v>
       </c>
       <c r="N7" t="n">
-        <v>9.875</v>
+        <v>10.8225</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1475</v>
+        <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>11.93</v>
+        <v>12.30375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2369</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1659</v>
+      </c>
+      <c r="E75" t="n">
+        <v>189</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>87</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>74</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4124137931034484</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.555555555555556</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-6.224489795918368</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
